--- a/engine/chart2/qa/extras/data/xlsx/color_funnel.xlsx
+++ b/engine/chart2/qa/extras/data/xlsx/color_funnel.xlsx
@@ -1,41 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\collabora\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A745F3D2-57A0-49B3-A904-AEFCE78BBB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="9240" windowHeight="6360" xr2:uid="{F16764EC-CFEF-4C31-B9AB-803B421B839B}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$B$3:$B$10</definedName>
+    <definedName function="false" hidden="true" name="_xlchart.v2.0" vbProcedure="false">Sheet1!$B$3:$B$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +72,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -55,25 +80,105 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF8B8B8B"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFC55A11"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF00B050"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -87,23 +192,29 @@
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
+    <cx:title>
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Colored funnel</cx:v>
+        </cx:txData>
+      </cx:tx>
       <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
+          <a:pPr>
+            <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1400" b="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>Colored funnel</a:t>
           </a:r>
@@ -112,28 +223,46 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{CA16CF20-B11C-4E3C-A882-1043E80435E6}">
+        <cx:series layoutId="funnel">
           <cx:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
+              <a:srgbClr val="C55A11"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="00B050"/>
               </a:solidFill>
+              <a:round/>
             </a:ln>
           </cx:spPr>
           <cx:dataLabels>
-            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+            <cx:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </cx:txPr>
+            <cx:separator>; </cx:separator>
           </cx:dataLabels>
           <cx:dataId val="0"/>
+          <cx:axisId val="1"/>
         </cx:series>
       </cx:plotAreaRegion>
       <cx:axis id="1">
-        <cx:catScaling gapWidth="0.0599999987"/>
+        <cx:catScaling gapWidth="0.6"/>
+        <cx:majorTickMarks type="none"/>
+        <cx:minorTickMarks type="none"/>
         <cx:tickLabels/>
+        <cx:numFmt formatCode="General" sourceLinked="1"/>
       </cx:axis>
     </cx:plotArea>
   </cx:chart>
@@ -148,35 +277,6 @@
   <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -186,36 +286,13 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -238,48 +315,13 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0">
@@ -287,7 +329,7 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <cs:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -297,428 +339,188 @@
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    <cs:fontRef idx="minor"/>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
+    <cs:fontRef idx="minor"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
+    <cs:fontRef idx="minor"/>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:fontRef idx="minor"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    <cs:fontRef idx="minor"/>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:colOff>343080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>6</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>37800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>76206</xdr:rowOff>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
-        <xdr:graphicFrame macro="">
+        <xdr:graphicFrame>
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Chart 1">
+            <xdr:cNvPr id="1" name="Chart 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5975985B-0039-8C17-585B-42F79751CDA8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{393D7C90-AF84-3958-641C-0FEC03FE8894}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
+            <a:off x="343080" y="0"/>
+            <a:ext cx="4424040" cy="2742840"/>
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
@@ -737,7 +539,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="342900" y="6"/>
+              <a:off x="6600825" y="2533650"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -757,7 +559,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -772,14 +574,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -814,7 +616,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -866,7 +668,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -918,49 +720,45 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -968,33 +766,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1007,13 +796,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1023,15 +806,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1039,7 +820,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1047,72 +827,74 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36160E35-1266-474B-9351-76E14A0F381F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B3:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>